--- a/outputs/tables/figure3B_table.xlsx
+++ b/outputs/tables/figure3B_table.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Stress_coupled</t>
+          <t>Stress_related</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
